--- a/Estimación de tareas/Tabla de Tareas V5 - Prescripciones Ortoprotesicas.xlsx
+++ b/Estimación de tareas/Tabla de Tareas V5 - Prescripciones Ortoprotesicas.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ClaudiaAlvarezDiaz\Documents\EJIE\Repo OSAKIDETZA\Osakidetza\Estimación de tareas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E8C11C-6B7A-4F25-9F7A-2428DB7393D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87BD1EC4-B42E-495D-B696-57F4A7E74DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C79E780C-2726-4F58-839C-D4F82C14C70B}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C79E780C-2726-4F58-839C-D4F82C14C70B}"/>
   </bookViews>
   <sheets>
     <sheet name="Tareas V5" sheetId="1" r:id="rId1"/>
     <sheet name="Resumen" sheetId="2" r:id="rId2"/>
-    <sheet name="Planificación" sheetId="9" r:id="rId3"/>
-    <sheet name="Cronograma" sheetId="10" r:id="rId4"/>
+    <sheet name="Planificación" sheetId="19" r:id="rId3"/>
+    <sheet name="Cronograma" sheetId="21" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tareas V5'!$A$1:$J$103</definedName>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="531">
   <si>
     <t>#</t>
   </si>
@@ -1076,12 +1076,6 @@
     <t>Resumen de Estimación — Prescripciones Ortoprotésicas V5</t>
   </si>
   <si>
-    <t>Fecha: 05/03/2026</t>
-  </si>
-  <si>
-    <t>Nota: Las Horas Estimadas incluyen un factor de riesgo (1.25x-1.50x) por desconocimiento de los sistemas de Osakidetza.</t>
-  </si>
-  <si>
     <t>Tareas</t>
   </si>
   <si>
@@ -1091,33 +1085,6 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>Comparativa con estimación original</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>o</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>i</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
     <t>Criterios de estimación aplicados</t>
   </si>
   <si>
@@ -1154,30 +1121,15 @@
     <t>Back-end</t>
   </si>
   <si>
-    <t>54,5 %</t>
-  </si>
-  <si>
     <t>Front-end</t>
   </si>
   <si>
-    <t>22,6 %</t>
-  </si>
-  <si>
-    <t>6,5 %</t>
-  </si>
-  <si>
     <t>Analista Funcional</t>
   </si>
   <si>
-    <t>9,2 %</t>
-  </si>
-  <si>
     <t>Project Manager</t>
   </si>
   <si>
-    <t>7,1 %</t>
-  </si>
-  <si>
     <t>TOTAL PROYECTO</t>
   </si>
   <si>
@@ -1220,12 +1172,6 @@
     <t>Roles principales</t>
   </si>
   <si>
-    <t>Fase 0: Arranque y Análisis</t>
-  </si>
-  <si>
-    <t>Toma contacto sistemas Osakidetza, resolución P-01 a P-08, diseño BBDD, arquitectura, especificaciones funcionales</t>
-  </si>
-  <si>
     <t>Fase 1: AUTH + CATÁLOGO</t>
   </si>
   <si>
@@ -1292,78 +1238,21 @@
     <t>PERSONAS ACTIVAS</t>
   </si>
   <si>
-    <t>Fase 0: Arranque</t>
-  </si>
-  <si>
-    <t>=</t>
-  </si>
-  <si>
     <t>Meses activos</t>
   </si>
   <si>
-    <t>3. Distribución por módulo (horas front/back)</t>
-  </si>
-  <si>
-    <t>Fase (9m)</t>
-  </si>
-  <si>
-    <t>Fase 1 (M2-M3)</t>
-  </si>
-  <si>
-    <t>Fase 1 (M2-M4)</t>
-  </si>
-  <si>
-    <t>Fase 2 (M3-M6)</t>
-  </si>
-  <si>
-    <t>Fase 3 (M5-M7)</t>
-  </si>
-  <si>
-    <t>Fase 4 (M6-M8)</t>
-  </si>
-  <si>
-    <t>4. Fases del proyecto (9 meses)</t>
-  </si>
-  <si>
-    <t>M2-M4</t>
-  </si>
-  <si>
-    <t>Autenticación (Osabide Global + externo), roles, catálogo completo (BBDD, sincronización, gestión, búsqueda, favoritos)</t>
-  </si>
-  <si>
-    <t>M3-M6</t>
-  </si>
-  <si>
-    <t>M5-M7</t>
-  </si>
-  <si>
     <t>Fase 4: MANT. + TRANSVERSAL</t>
   </si>
   <si>
-    <t>M6-M8</t>
-  </si>
-  <si>
     <t>Fase 5: QA integral + Estabiliz.</t>
   </si>
   <si>
     <t>M7-M9</t>
   </si>
   <si>
-    <t>Pruebas integración E2E, corrección defectos, pruebas de aceptación con Osakidetza</t>
-  </si>
-  <si>
-    <t>6. Riesgos que afectan al cronograma</t>
-  </si>
-  <si>
     <t>Complejidad máquinas de estados</t>
   </si>
   <si>
-    <t>Desglose por Fases (9 meses)</t>
-  </si>
-  <si>
-    <t>Fase 1: AUTH+CATÁLOGO</t>
-  </si>
-  <si>
     <t>Fase 3: DISP.+TAREAS</t>
   </si>
   <si>
@@ -1373,222 +1262,45 @@
     <t>Fase 5: QA+Estabiliz.</t>
   </si>
   <si>
-    <t>Planificación del Equipo — Prescripciones Ortoprotésicas V5 (9 meses, 155 h/mes)</t>
-  </si>
-  <si>
-    <t>Fecha: 05/03/2026 | Jornada: 155 h/mes (tiempo completo) | Horas técnicas: 3686 h | Total proyecto: 4404 h</t>
-  </si>
-  <si>
     <t>Horas</t>
   </si>
   <si>
     <t>% total</t>
   </si>
   <si>
-    <t>100% (M1-M9)</t>
-  </si>
-  <si>
-    <t>2 Seniors TC: APIs, BBDD, integraciones, máq. estados (~1200 h/pers., util. 86%)</t>
-  </si>
-  <si>
-    <t>1 Senior TC: pantallas, formularios, UX, firma digital (util. 71%)</t>
-  </si>
-  <si>
-    <t>31% (M4-M9)</t>
-  </si>
-  <si>
-    <t>1 persona parcial (~1.9 meses-persona): unitarias, integración, E2E. Arranca M4, 100% desde M6</t>
-  </si>
-  <si>
-    <t>29% (M1-M9)</t>
-  </si>
-  <si>
-    <t>1 persona parcial (~2.6 meses-persona): especificaciones, validación flujos, aceptación</t>
-  </si>
-  <si>
-    <t>22% (M1-M9)</t>
-  </si>
-  <si>
-    <t>1 persona parcial (~2 meses-persona): planificación, seguimiento, riesgos, coordinación</t>
-  </si>
-  <si>
-    <t>3 TC + 3 parcial</t>
-  </si>
-  <si>
-    <t>Esfuerzo técnico (3686 h) + gestión (718 h)</t>
-  </si>
-  <si>
-    <t>2. Composición del equipo (9 meses, 155 h/mes)</t>
-  </si>
-  <si>
-    <t>Desarrolladores a tiempo completo (155 h/mes). QA, AF y PM con dedicación parcial. Capacidad 9 meses: 1395 h/persona.</t>
-  </si>
-  <si>
     <t>Horas asignadas</t>
   </si>
   <si>
     <t>h/mes efectivas</t>
   </si>
   <si>
-    <t>Utilización</t>
-  </si>
-  <si>
-    <t>M1-M9 (9m)</t>
-  </si>
-  <si>
-    <t>AUTH (back) + PRESCRIPCIÓN (back) + TRANSVERSAL. APIs, BBDD, integraciones Osabide Global, Giltza</t>
-  </si>
-  <si>
-    <t>CATÁLOGO (back) + DISPENSACIÓN + TAREAS + MANTENIMIENTO. Nomenclátor, visado, SOA, máq. estados</t>
-  </si>
-  <si>
     <t>Todas las pantallas: prescripción, catálogo, listados, firma, dispensación, mantenimiento</t>
   </si>
   <si>
-    <t>M4-M9 (6m)</t>
-  </si>
-  <si>
-    <t>31% media</t>
-  </si>
-  <si>
-    <t>Arranca M4 con unitarias; pico M6-M8 con integración E2E y aceptación</t>
-  </si>
-  <si>
-    <t>29% media</t>
-  </si>
-  <si>
-    <t>Fuerte M1-M3 (especificaciones, flujos); decrece M4-M7; repunta M8-M9 (validación aceptación)</t>
-  </si>
-  <si>
-    <t>22% media</t>
-  </si>
-  <si>
-    <t>Coordinación continua; picos en arranque (M1) y cierre (M8-M9)</t>
-  </si>
-  <si>
-    <t>Pico: 6 pers. (M4-M8); Medio: 5,3 pers.</t>
-  </si>
-  <si>
-    <t>PM, AF, Back ×2</t>
-  </si>
-  <si>
-    <t>Back ×2, Front, AF</t>
-  </si>
-  <si>
     <t>Back ×2, Front, QA</t>
   </si>
   <si>
-    <t>QA, Back ×1, Front, AF</t>
-  </si>
-  <si>
-    <t>5. Capacidad vs Demanda (155 h/persona/mes)</t>
-  </si>
-  <si>
-    <t>Capacidad 9m</t>
-  </si>
-  <si>
-    <t>Horas necesarias</t>
-  </si>
-  <si>
-    <t>Holgura</t>
-  </si>
-  <si>
-    <t>Observación</t>
-  </si>
-  <si>
-    <t>Back-end (2 × 9m)</t>
-  </si>
-  <si>
-    <t>Holgura de 389 h para imprevistos, unknowns y soporte QA</t>
-  </si>
-  <si>
-    <t>Front-end (1 × 9m)</t>
-  </si>
-  <si>
-    <t>Holgura de 398 h: apoyo a QA funcional y maquetación extra</t>
-  </si>
-  <si>
-    <t>QA (1 × 6m, M4-M9)</t>
-  </si>
-  <si>
-    <t>Holgura de 642 h: pruebas de regresión y aceptación</t>
-  </si>
-  <si>
-    <t>AF (parcial, 9m)</t>
-  </si>
-  <si>
-    <t>Dedicación variable: alta M1-M3, media M4-M7, alta M8-M9</t>
-  </si>
-  <si>
-    <t>PM (parcial, 9m)</t>
-  </si>
-  <si>
-    <t>Dedicación constante ~2 h/mes, picos en M1 y M9</t>
-  </si>
-  <si>
     <t>Impacto</t>
   </si>
   <si>
     <t>Retraso acceso sistemas Osakidetza</t>
   </si>
   <si>
-    <t>+1-2 meses si no se resuelve en M1</t>
-  </si>
-  <si>
-    <t>Solicitar accesos primera semana de M1</t>
-  </si>
-  <si>
     <t>Preguntas abiertas P-01 a P-08</t>
   </si>
   <si>
-    <t>Bloqueo de módulos completos</t>
-  </si>
-  <si>
-    <t>Resolución obligatoria en Fase 0</t>
-  </si>
-  <si>
     <t>APIs interoperabilidad (visado)</t>
   </si>
   <si>
     <t>Retraso Fase 3 (+1 mes)</t>
   </si>
   <si>
-    <t>Desarrollo mock-first, contrato API temprano</t>
-  </si>
-  <si>
     <t>Desbordamiento PRESCRIPCIÓN (+2 sem.)</t>
   </si>
   <si>
-    <t>Prototipo funcional en M4 para validación</t>
-  </si>
-  <si>
     <t>Baja de un Back Senior</t>
   </si>
   <si>
-    <t>-1 persona → Back puro sube a 1.395h/pers., inviable</t>
-  </si>
-  <si>
-    <t>Tener candidato backup identificado; documentación cruzada</t>
-  </si>
-  <si>
-    <t>Front con holgura alta (28%)</t>
-  </si>
-  <si>
-    <t>Subocupación del recurso entre M8-M9</t>
-  </si>
-  <si>
-    <t>Asignar tareas QA funcionales + documentación técnica</t>
-  </si>
-  <si>
-    <t>Cronograma — Prescripciones Ortoprotésicas Osakidetza (9 meses, 155 h/mes)</t>
-  </si>
-  <si>
-    <t>Equipo: 6 personas (3 TC + 3 parciales) | Técnico: 3686 h | Total: 4404 h</t>
-  </si>
-  <si>
-    <t>Rol / Dedicación</t>
-  </si>
-  <si>
     <t>Back-end Senior 1 (TC)</t>
   </si>
   <si>
@@ -1598,10 +1310,331 @@
     <t>Front-end Senior (TC)</t>
   </si>
   <si>
-    <t>QA (parcial)</t>
-  </si>
-  <si>
-    <t>CAPACIDAD (155h × activos)</t>
+    <t>Arquitecto</t>
+  </si>
+  <si>
+    <t>UX/Diseño</t>
+  </si>
+  <si>
+    <t>Planificación, seguimiento, riesgos, coordinación Osakidetza, gestión entregas</t>
+  </si>
+  <si>
+    <t>M1-M2 (2m)</t>
+  </si>
+  <si>
+    <t>3. Distribución por módulo (horas front/back de tareas)</t>
+  </si>
+  <si>
+    <t>M1-M2</t>
+  </si>
+  <si>
+    <t>Autenticación (Osabide Global + externo), roles, catálogo completo (BBDD, sincronización, búsqueda, favoritos)</t>
+  </si>
+  <si>
+    <t>Pruebas integración E2E completas, corrección defectos, pruebas de aceptación con Osakidetza</t>
+  </si>
+  <si>
+    <t>QA, Back ×1, Front, AF, PM</t>
+  </si>
+  <si>
+    <t>5. Riesgos que afectan al cronograma</t>
+  </si>
+  <si>
+    <t>Back puro sube a 2.401h/1 persona: inviable</t>
+  </si>
+  <si>
+    <t>QA (TC)</t>
+  </si>
+  <si>
+    <t>Planificación del Equipo — Prescripciones Ortoprotésicas V5 (11 meses, 155 h/mes)</t>
+  </si>
+  <si>
+    <t>TC (M3-M11)</t>
+  </si>
+  <si>
+    <t>M3 full + M4 parcial</t>
+  </si>
+  <si>
+    <t>Arquitectura, diseño técnico, decisiones tecnológicas M3; revisión código y guía M4. Total 180h</t>
+  </si>
+  <si>
+    <t>TC (M1-M2)</t>
+  </si>
+  <si>
+    <t>Diseño de interacción, wireframes, prototipado M1-M2. Entrega diseño completo antes de M3</t>
+  </si>
+  <si>
+    <t>1 persona TC: unitarias desde M3, integración desde M5, E2E desde M7, aceptación M9-M11 (1395 h)</t>
+  </si>
+  <si>
+    <t>Parcial (M1-M11)</t>
+  </si>
+  <si>
+    <t>Arranca M1 en paralelo con UX: especificaciones, flujos, toma requisitos. Apoyo continuo hasta M11</t>
+  </si>
+  <si>
+    <t>2. Composición del equipo (11 meses, 155 h/mes)</t>
+  </si>
+  <si>
+    <t>Análisis y Diseño</t>
+  </si>
+  <si>
+    <t>Wireframes, prototipado, diseño de interacción. Entrega guía visual completa en M2 para que Front arranque en M3</t>
+  </si>
+  <si>
+    <t>M1-M11 (11m)</t>
+  </si>
+  <si>
+    <t>Análisis → Desarrollo</t>
+  </si>
+  <si>
+    <t>Arranca M1 con UX: especificaciones funcionales, flujos, toma requisitos con Osakidetza. Apoyo continuo M3-M11</t>
+  </si>
+  <si>
+    <t>Coordinación continua</t>
+  </si>
+  <si>
+    <t>Coordinación global; picos en arranque (M1-M2) y cierre (M10-M11)</t>
+  </si>
+  <si>
+    <t>M3-M4 (2m)</t>
+  </si>
+  <si>
+    <t>Arranque desarrollo</t>
+  </si>
+  <si>
+    <t>M3: arquitectura, diseño BBDD, definición APIs, stack tecnológico (155h). M4: revisión código, guía equipo (25h)</t>
+  </si>
+  <si>
+    <t>M3-M11 (9m)</t>
+  </si>
+  <si>
+    <t>Desarrollo</t>
+  </si>
+  <si>
+    <t>QA continuo</t>
+  </si>
+  <si>
+    <t>TC desde M3: unitarias, integración desde M5, E2E desde M7, aceptación con Osakidetza M9-M11</t>
+  </si>
+  <si>
+    <t>Fase desarrollo</t>
+  </si>
+  <si>
+    <t>Fase 1 (M4-M5)</t>
+  </si>
+  <si>
+    <t>Fase 1 (M4-M6)</t>
+  </si>
+  <si>
+    <t>Fase 2 (M5-M8)</t>
+  </si>
+  <si>
+    <t>Fase 3 (M7-M9)</t>
+  </si>
+  <si>
+    <t>Fase 4 (M8-M10)</t>
+  </si>
+  <si>
+    <t>4. Fases del proyecto (11 meses)</t>
+  </si>
+  <si>
+    <t>Fase 0: Análisis + Diseño UX</t>
+  </si>
+  <si>
+    <t>Diseño UX completo (wireframes, prototipos), toma requisitos funcionales, especificaciones AF, resolución preguntas abiertas P-01 a P-08</t>
+  </si>
+  <si>
+    <t>UX, AF, PM</t>
+  </si>
+  <si>
+    <t>Fase 0B: Arranque técnico</t>
+  </si>
+  <si>
+    <t>Arquitectura, diseño BBDD, stack técnico, setup entorno, pipelines CI/CD. Primeros sprints dev</t>
+  </si>
+  <si>
+    <t>Arq, Back ×2, Front, QA, AF, PM</t>
+  </si>
+  <si>
+    <t>M4-M6</t>
+  </si>
+  <si>
+    <t>Back ×2, Front, QA, AF</t>
+  </si>
+  <si>
+    <t>M5-M8</t>
+  </si>
+  <si>
+    <t>M8-M10</t>
+  </si>
+  <si>
+    <t>M9-M11</t>
+  </si>
+  <si>
+    <t>+1-2 meses retraso desarrollo</t>
+  </si>
+  <si>
+    <t>Solicitar accesos en M1 aprovechando fase análisis</t>
+  </si>
+  <si>
+    <t>Bloqueo módulos completos desde M3</t>
+  </si>
+  <si>
+    <t>Resolución obligatoria en M1-M2 (fase análisis)</t>
+  </si>
+  <si>
+    <t>Diseño UX no validado en M2</t>
+  </si>
+  <si>
+    <t>Retraso arranque desarrollo: Front sin diseño</t>
+  </si>
+  <si>
+    <t>UX entrega wireframes iterativos; validación con stakeholders en M2</t>
+  </si>
+  <si>
+    <t>Desarrollo mock-first, contrato API definido en M3</t>
+  </si>
+  <si>
+    <t>Prototipo funcional en M6 para validación temprana</t>
+  </si>
+  <si>
+    <t>Candidato backup; documentación cruzada Back 1 ↔ 2</t>
+  </si>
+  <si>
+    <t>QA encuentra defectos críticos en M9+</t>
+  </si>
+  <si>
+    <t>Retrabajo M10-M11, posible mes 12</t>
+  </si>
+  <si>
+    <t>QA integrado desde M3: detección temprana, ciclos cortos</t>
+  </si>
+  <si>
+    <t>M10</t>
+  </si>
+  <si>
+    <t>M11</t>
+  </si>
+  <si>
+    <t>Desglose por Fases (11 meses)</t>
+  </si>
+  <si>
+    <t>Cronograma - Prescripciones Ortoprotesicas Osakidetza (11 meses, 155 h/mes)</t>
+  </si>
+  <si>
+    <t>M1-M2: Analisis + UX | M3-M11: Desarrollo + QA | Equipo pico: 7 pers. (M3-M4) | Total: 5880 h</t>
+  </si>
+  <si>
+    <t>Rol / Dedicacion</t>
+  </si>
+  <si>
+    <t>% proy.</t>
+  </si>
+  <si>
+    <t>UX/Diseno (TC)</t>
+  </si>
+  <si>
+    <t>--- Fase analisis ---|--- Fase desarrollo + QA ---</t>
+  </si>
+  <si>
+    <t>Fase 0: Analisis+UX</t>
+  </si>
+  <si>
+    <t>Fase 0B: Arranque tec.</t>
+  </si>
+  <si>
+    <t>Fase 1: AUTH+CATALOGO</t>
+  </si>
+  <si>
+    <t>Fase 2: PRESCRIPCION</t>
+  </si>
+  <si>
+    <t>Fecha: 06/03/2026</t>
+  </si>
+  <si>
+    <t>Comparativa con estimacion original</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Tareas Excel original (referencia)</t>
+  </si>
+  <si>
+    <t>Tareas conservadas en V5</t>
+  </si>
+  <si>
+    <t>Tareas nuevas en V5</t>
+  </si>
+  <si>
+    <t>Total tareas V5</t>
+  </si>
+  <si>
+    <t>Horas Excel original (referencia)</t>
+  </si>
+  <si>
+    <t>Horas estimadas V5 (tareas tecnicas)</t>
+  </si>
+  <si>
+    <t>Diferencia vs original</t>
+  </si>
+  <si>
+    <t>Incremento tareas</t>
+  </si>
+  <si>
+    <t>Total proyecto V5 (incl. gestion, QA, UX, Arq)</t>
+  </si>
+  <si>
+    <t>Fecha: 06/03/2026 | Jornada: 155 h/mes (TC) | Horas tareas: 3686 h | Total proyecto: 5880 h</t>
+  </si>
+  <si>
+    <t>Pico 7 (M3-M4)</t>
+  </si>
+  <si>
+    <t>M1-M2: Fase de analisis y diseno UX (3 personas). M3-M11: Desarrollo + QA (hasta 7 personas en M3-M4).</t>
+  </si>
+  <si>
+    <t>Pico: 7 pers. (M3-M4); 3 pers. (M1-M2); 6 pers. (M5-M11)</t>
+  </si>
+  <si>
+    <t>Nota: Las Horas Estimadas incluyen un factor de riesgo uniforme (1.30x) aplicado sobre la base estimada de cada tarea.</t>
+  </si>
+  <si>
+    <t>+1.698 h</t>
+  </si>
+  <si>
+    <t>42,2 %</t>
+  </si>
+  <si>
+    <t>2 Seniors TC: APIs, BBDD, integraciones Osabide/Osategi/Giltza, maq. estados (~1364 h/pers., util. 97,8%)</t>
+  </si>
+  <si>
+    <t>19,4 %</t>
+  </si>
+  <si>
+    <t>1 Senior TC: pantallas, formularios, componentes, UX, firma digital (util. 89,6%)</t>
+  </si>
+  <si>
+    <t>2,8 %</t>
+  </si>
+  <si>
+    <t>4,8 %</t>
+  </si>
+  <si>
+    <t>18,6 %</t>
+  </si>
+  <si>
+    <t>5,4 %</t>
+  </si>
+  <si>
+    <t>6,8 %</t>
+  </si>
+  <si>
+    <t>AUTH (back) + PRESCRIPCION (back) + TRANSVERSAL. APIs, BBDD, integraciones Osabide Global, Giltza</t>
+  </si>
+  <si>
+    <t>CATALOGO (back) + DISPENSACION + TAREAS + MANTENIMIENTO. Nomenclator, visado, SOA, maq. estados</t>
   </si>
 </sst>
 </file>
@@ -1675,14 +1708,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1751,43 +1785,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
+        <fgColor rgb="FF00008B"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF70AD47"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED7D31"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5B9BD5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BBB59"/>
+        <fgColor rgb="FF90EE90"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1819,7 +1823,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1969,60 +1973,23 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2429,7 +2396,7 @@
         <v>40</v>
       </c>
       <c r="I2" s="5">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J2" s="24" t="s">
         <v>16</v>
@@ -2457,7 +2424,7 @@
       <c r="G3" s="3"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J3" s="24" t="s">
         <v>19</v>
@@ -2489,7 +2456,7 @@
         <v>30</v>
       </c>
       <c r="I4" s="5">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J4" s="24"/>
     </row>
@@ -2519,7 +2486,7 @@
         <v>60</v>
       </c>
       <c r="I5" s="5">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J5" s="24" t="s">
         <v>25</v>
@@ -2547,7 +2514,7 @@
       <c r="G6" s="3"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J6" s="24" t="s">
         <v>29</v>
@@ -2575,7 +2542,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="5"/>
       <c r="I7" s="5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J7" s="24" t="s">
         <v>29</v>
@@ -2603,7 +2570,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="5"/>
       <c r="I8" s="5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J8" s="24" t="s">
         <v>33</v>
@@ -2631,7 +2598,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="5"/>
       <c r="I9" s="5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J9" s="24" t="s">
         <v>33</v>
@@ -2659,7 +2626,7 @@
       <c r="G10" s="3"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J10" s="24" t="s">
         <v>38</v>
@@ -2687,7 +2654,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J11" s="24" t="s">
         <v>33</v>
@@ -2719,7 +2686,7 @@
         <v>40</v>
       </c>
       <c r="I12" s="8">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J12" s="25"/>
     </row>
@@ -2749,7 +2716,7 @@
         <v>20</v>
       </c>
       <c r="I13" s="8">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J13" s="25"/>
     </row>
@@ -2775,7 +2742,7 @@
       <c r="G14" s="6"/>
       <c r="H14" s="8"/>
       <c r="I14" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J14" s="25" t="s">
         <v>49</v>
@@ -2807,7 +2774,7 @@
         <v>40</v>
       </c>
       <c r="I15" s="8">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J15" s="25" t="s">
         <v>54</v>
@@ -2839,7 +2806,7 @@
         <v>20</v>
       </c>
       <c r="I16" s="8">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J16" s="25"/>
     </row>
@@ -2865,7 +2832,7 @@
       <c r="G17" s="6"/>
       <c r="H17" s="8"/>
       <c r="I17" s="8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J17" s="25" t="s">
         <v>60</v>
@@ -2897,7 +2864,7 @@
         <v>40</v>
       </c>
       <c r="I18" s="8">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J18" s="25"/>
     </row>
@@ -2927,7 +2894,7 @@
         <v>60</v>
       </c>
       <c r="I19" s="8">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="J19" s="25"/>
     </row>
@@ -2957,7 +2924,7 @@
         <v>40</v>
       </c>
       <c r="I20" s="8">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J20" s="25"/>
     </row>
@@ -2987,7 +2954,7 @@
         <v>20</v>
       </c>
       <c r="I21" s="8">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J21" s="25"/>
     </row>
@@ -3017,7 +2984,7 @@
         <v>20</v>
       </c>
       <c r="I22" s="8">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J22" s="25"/>
     </row>
@@ -3047,7 +3014,7 @@
         <v>20</v>
       </c>
       <c r="I23" s="8">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J23" s="25"/>
     </row>
@@ -3073,7 +3040,7 @@
       <c r="G24" s="6"/>
       <c r="H24" s="8"/>
       <c r="I24" s="8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J24" s="25" t="s">
         <v>33</v>
@@ -3105,7 +3072,7 @@
         <v>40</v>
       </c>
       <c r="I25" s="8">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J25" s="25"/>
     </row>
@@ -3131,7 +3098,7 @@
       <c r="G26" s="6"/>
       <c r="H26" s="8"/>
       <c r="I26" s="8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J26" s="25" t="s">
         <v>33</v>
@@ -3159,7 +3126,7 @@
       <c r="G27" s="6"/>
       <c r="H27" s="8"/>
       <c r="I27" s="8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J27" s="25" t="s">
         <v>33</v>
@@ -3191,7 +3158,7 @@
         <v>40</v>
       </c>
       <c r="I28" s="8">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J28" s="25"/>
     </row>
@@ -3221,7 +3188,7 @@
         <v>30</v>
       </c>
       <c r="I29" s="8">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J29" s="25"/>
     </row>
@@ -3251,7 +3218,7 @@
         <v>40</v>
       </c>
       <c r="I30" s="11">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J30" s="26" t="s">
         <v>100</v>
@@ -3283,7 +3250,7 @@
         <v>20</v>
       </c>
       <c r="I31" s="11">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J31" s="26"/>
     </row>
@@ -3313,7 +3280,7 @@
         <v>40</v>
       </c>
       <c r="I32" s="11">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J32" s="26"/>
     </row>
@@ -3343,7 +3310,7 @@
         <v>60</v>
       </c>
       <c r="I33" s="11">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J33" s="26" t="s">
         <v>110</v>
@@ -3371,7 +3338,7 @@
       <c r="G34" s="9"/>
       <c r="H34" s="11"/>
       <c r="I34" s="11">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J34" s="26" t="s">
         <v>33</v>
@@ -3403,7 +3370,7 @@
         <v>20</v>
       </c>
       <c r="I35" s="11">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J35" s="26"/>
     </row>
@@ -3433,7 +3400,7 @@
         <v>40</v>
       </c>
       <c r="I36" s="11">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J36" s="26"/>
     </row>
@@ -3459,7 +3426,7 @@
       <c r="G37" s="9"/>
       <c r="H37" s="11"/>
       <c r="I37" s="11">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J37" s="26" t="s">
         <v>33</v>
@@ -3487,7 +3454,7 @@
       <c r="G38" s="9"/>
       <c r="H38" s="11"/>
       <c r="I38" s="11">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J38" s="26" t="s">
         <v>33</v>
@@ -3515,7 +3482,7 @@
       <c r="G39" s="9"/>
       <c r="H39" s="11"/>
       <c r="I39" s="11">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J39" s="26" t="s">
         <v>33</v>
@@ -3547,7 +3514,7 @@
         <v>40</v>
       </c>
       <c r="I40" s="11">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J40" s="26"/>
     </row>
@@ -3577,7 +3544,7 @@
         <v>40</v>
       </c>
       <c r="I41" s="11">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J41" s="26" t="s">
         <v>132</v>
@@ -3609,7 +3576,7 @@
         <v>40</v>
       </c>
       <c r="I42" s="11">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J42" s="26" t="s">
         <v>136</v>
@@ -3641,7 +3608,7 @@
         <v>20</v>
       </c>
       <c r="I43" s="11">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J43" s="26"/>
     </row>
@@ -3671,7 +3638,7 @@
         <v>20</v>
       </c>
       <c r="I44" s="11">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J44" s="26"/>
     </row>
@@ -3701,7 +3668,7 @@
         <v>20</v>
       </c>
       <c r="I45" s="11">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J45" s="26" t="s">
         <v>146</v>
@@ -3729,7 +3696,7 @@
       <c r="G46" s="9"/>
       <c r="H46" s="11"/>
       <c r="I46" s="11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J46" s="26" t="s">
         <v>149</v>
@@ -3757,7 +3724,7 @@
       <c r="G47" s="9"/>
       <c r="H47" s="11"/>
       <c r="I47" s="11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J47" s="26" t="s">
         <v>33</v>
@@ -3785,7 +3752,7 @@
       <c r="G48" s="9"/>
       <c r="H48" s="11"/>
       <c r="I48" s="11">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J48" s="26" t="s">
         <v>154</v>
@@ -3813,7 +3780,7 @@
       <c r="G49" s="9"/>
       <c r="H49" s="11"/>
       <c r="I49" s="11">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J49" s="26" t="s">
         <v>157</v>
@@ -3845,7 +3812,7 @@
         <v>10</v>
       </c>
       <c r="I50" s="11">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J50" s="26" t="s">
         <v>162</v>
@@ -3877,7 +3844,7 @@
         <v>40</v>
       </c>
       <c r="I51" s="11">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J51" s="26" t="s">
         <v>166</v>
@@ -3909,7 +3876,7 @@
         <v>40</v>
       </c>
       <c r="I52" s="11">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J52" s="26"/>
     </row>
@@ -3939,7 +3906,7 @@
         <v>40</v>
       </c>
       <c r="I53" s="11">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J53" s="26"/>
     </row>
@@ -3969,7 +3936,7 @@
         <v>40</v>
       </c>
       <c r="I54" s="11">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J54" s="26"/>
     </row>
@@ -4027,7 +3994,7 @@
         <v>40</v>
       </c>
       <c r="I56" s="11">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J56" s="26" t="s">
         <v>183</v>
@@ -4087,7 +4054,7 @@
         <v>20</v>
       </c>
       <c r="I58" s="11">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J58" s="26"/>
     </row>
@@ -4145,7 +4112,7 @@
         <v>30</v>
       </c>
       <c r="I60" s="11">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J60" s="26"/>
     </row>
@@ -4171,7 +4138,7 @@
       <c r="G61" s="9"/>
       <c r="H61" s="11"/>
       <c r="I61" s="11">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J61" s="26" t="s">
         <v>33</v>
@@ -4203,7 +4170,7 @@
         <v>40</v>
       </c>
       <c r="I62" s="11">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J62" s="26"/>
     </row>
@@ -4229,7 +4196,7 @@
       <c r="G63" s="9"/>
       <c r="H63" s="11"/>
       <c r="I63" s="11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J63" s="26" t="s">
         <v>202</v>
@@ -4257,7 +4224,7 @@
       <c r="G64" s="9"/>
       <c r="H64" s="11"/>
       <c r="I64" s="11">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J64" s="26" t="s">
         <v>33</v>
@@ -4317,7 +4284,7 @@
         <v>10</v>
       </c>
       <c r="I66" s="11">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J66" s="26"/>
     </row>
@@ -4347,7 +4314,7 @@
         <v>30</v>
       </c>
       <c r="I67" s="11">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J67" s="26" t="s">
         <v>214</v>
@@ -4379,7 +4346,7 @@
         <v>40</v>
       </c>
       <c r="I68" s="11">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J68" s="26"/>
     </row>
@@ -4409,7 +4376,7 @@
         <v>60</v>
       </c>
       <c r="I69" s="11">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="J69" s="26"/>
     </row>
@@ -4439,7 +4406,7 @@
         <v>20</v>
       </c>
       <c r="I70" s="11">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J70" s="26" t="s">
         <v>226</v>
@@ -4467,7 +4434,7 @@
       <c r="G71" s="9"/>
       <c r="H71" s="11"/>
       <c r="I71" s="11">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J71" s="32" t="s">
         <v>230</v>
@@ -4495,7 +4462,7 @@
       <c r="G72" s="9"/>
       <c r="H72" s="11"/>
       <c r="I72" s="11">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J72" s="32" t="s">
         <v>233</v>
@@ -4523,7 +4490,7 @@
       <c r="G73" s="9"/>
       <c r="H73" s="11"/>
       <c r="I73" s="11">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J73" s="26" t="s">
         <v>237</v>
@@ -4551,7 +4518,7 @@
       <c r="G74" s="9"/>
       <c r="H74" s="11"/>
       <c r="I74" s="11">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J74" s="26" t="s">
         <v>241</v>
@@ -4583,7 +4550,7 @@
         <v>40</v>
       </c>
       <c r="I75" s="14">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J75" s="27" t="s">
         <v>247</v>
@@ -4615,7 +4582,7 @@
         <v>30</v>
       </c>
       <c r="I76" s="14">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J76" s="27" t="s">
         <v>251</v>
@@ -4647,7 +4614,7 @@
         <v>30</v>
       </c>
       <c r="I77" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J77" s="27"/>
     </row>
@@ -4677,7 +4644,7 @@
         <v>60</v>
       </c>
       <c r="I78" s="14">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J78" s="27" t="s">
         <v>258</v>
@@ -4705,7 +4672,7 @@
       <c r="G79" s="12"/>
       <c r="H79" s="14"/>
       <c r="I79" s="14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J79" s="27" t="s">
         <v>262</v>
@@ -4737,7 +4704,7 @@
         <v>60</v>
       </c>
       <c r="I80" s="14">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J80" s="27" t="s">
         <v>266</v>
@@ -4765,7 +4732,7 @@
       <c r="G81" s="12"/>
       <c r="H81" s="14"/>
       <c r="I81" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J81" s="27" t="s">
         <v>33</v>
@@ -4793,7 +4760,7 @@
       <c r="G82" s="12"/>
       <c r="H82" s="14"/>
       <c r="I82" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J82" s="27" t="s">
         <v>33</v>
@@ -4821,7 +4788,7 @@
       <c r="G83" s="12"/>
       <c r="H83" s="14"/>
       <c r="I83" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J83" s="27" t="s">
         <v>274</v>
@@ -4849,7 +4816,7 @@
       <c r="G84" s="12"/>
       <c r="H84" s="14"/>
       <c r="I84" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J84" s="27" t="s">
         <v>33</v>
@@ -4881,7 +4848,7 @@
         <v>30</v>
       </c>
       <c r="I85" s="17">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J85" s="28"/>
     </row>
@@ -4911,7 +4878,7 @@
         <v>30</v>
       </c>
       <c r="I86" s="17">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J86" s="28"/>
     </row>
@@ -4937,7 +4904,7 @@
       <c r="G87" s="15"/>
       <c r="H87" s="17"/>
       <c r="I87" s="17">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J87" s="28" t="s">
         <v>33</v>
@@ -4965,7 +4932,7 @@
       <c r="G88" s="15"/>
       <c r="H88" s="17"/>
       <c r="I88" s="17">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J88" s="28" t="s">
         <v>33</v>
@@ -4997,7 +4964,7 @@
         <v>40</v>
       </c>
       <c r="I89" s="17">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J89" s="28"/>
     </row>
@@ -5027,7 +4994,7 @@
         <v>40</v>
       </c>
       <c r="I90" s="17">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J90" s="28"/>
     </row>
@@ -5053,7 +5020,7 @@
       <c r="G91" s="15"/>
       <c r="H91" s="17"/>
       <c r="I91" s="17">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J91" s="28" t="s">
         <v>33</v>
@@ -5081,7 +5048,7 @@
       <c r="G92" s="15"/>
       <c r="H92" s="17"/>
       <c r="I92" s="17">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J92" s="28" t="s">
         <v>33</v>
@@ -5109,7 +5076,7 @@
       <c r="G93" s="18"/>
       <c r="H93" s="20"/>
       <c r="I93" s="20">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J93" s="29" t="s">
         <v>33</v>
@@ -5137,7 +5104,7 @@
       <c r="G94" s="18"/>
       <c r="H94" s="20"/>
       <c r="I94" s="20">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J94" s="29" t="s">
         <v>33</v>
@@ -5165,7 +5132,7 @@
       <c r="G95" s="18"/>
       <c r="H95" s="20"/>
       <c r="I95" s="20">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J95" s="29" t="s">
         <v>308</v>
@@ -5197,7 +5164,7 @@
         <v>40</v>
       </c>
       <c r="I96" s="20">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J96" s="29" t="s">
         <v>312</v>
@@ -5229,7 +5196,7 @@
         <v>60</v>
       </c>
       <c r="I97" s="23">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="J97" s="30" t="s">
         <v>318</v>
@@ -5261,7 +5228,7 @@
         <v>60</v>
       </c>
       <c r="I98" s="23">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="J98" s="30"/>
     </row>
@@ -5287,7 +5254,7 @@
       <c r="G99" s="21"/>
       <c r="H99" s="23"/>
       <c r="I99" s="23">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J99" s="30" t="s">
         <v>324</v>
@@ -5319,7 +5286,7 @@
         <v>40</v>
       </c>
       <c r="I100" s="23">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J100" s="30" t="s">
         <v>329</v>
@@ -5351,7 +5318,7 @@
         <v>120</v>
       </c>
       <c r="I101" s="23">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="J101" s="30" t="s">
         <v>334</v>
@@ -5383,7 +5350,7 @@
         <v>120</v>
       </c>
       <c r="I102" s="23">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="J102" s="30"/>
     </row>
@@ -5440,23 +5407,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="68" t="s">
         <v>343</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>344</v>
+        <v>502</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>345</v>
+        <v>518</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -5464,7 +5431,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C5" s="34" t="s">
         <v>14</v>
@@ -5479,7 +5446,7 @@
         <v>8</v>
       </c>
       <c r="G5" s="34" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -5499,10 +5466,10 @@
         <v>130</v>
       </c>
       <c r="F6" s="3">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="G6" s="36">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -5522,10 +5489,10 @@
         <v>430</v>
       </c>
       <c r="F7" s="6">
-        <v>610</v>
+        <v>682</v>
       </c>
       <c r="G7" s="37">
-        <v>0.42</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -5545,10 +5512,10 @@
         <v>860</v>
       </c>
       <c r="F8" s="9">
-        <v>1464</v>
+        <v>1583</v>
       </c>
       <c r="G8" s="38">
-        <v>0.7</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
@@ -5568,10 +5535,10 @@
         <v>220</v>
       </c>
       <c r="F9" s="12">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="G9" s="39">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -5591,10 +5558,10 @@
         <v>140</v>
       </c>
       <c r="F10" s="15">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="G10" s="40">
-        <v>0.74</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -5614,10 +5581,10 @@
         <v>40</v>
       </c>
       <c r="F11" s="18">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="G11" s="41">
-        <v>2.0299999999999998</v>
+        <v>2.2799999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -5637,15 +5604,15 @@
         <v>460</v>
       </c>
       <c r="F12" s="21">
-        <v>528</v>
+        <v>572</v>
       </c>
       <c r="G12" s="42">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="35" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B13" s="34">
         <v>102</v>
@@ -5660,189 +5627,187 @@
         <v>2280</v>
       </c>
       <c r="F13" s="34">
-        <v>3686</v>
+        <v>3978</v>
       </c>
       <c r="G13" s="43">
-        <v>0.62</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="16" x14ac:dyDescent="0.4">
-      <c r="A16" s="74" t="s">
-        <v>349</v>
-      </c>
-      <c r="B16" s="74"/>
-      <c r="C16" s="74"/>
-      <c r="D16" s="74"/>
+      <c r="A16" s="59" t="s">
+        <v>503</v>
+      </c>
+      <c r="B16" s="59"/>
+      <c r="C16" s="59"/>
+      <c r="D16" s="59"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="B17" t="s">
-        <v>351</v>
+        <v>357</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="1">
+      <c r="A18" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B18">
         <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="B19" t="s">
-        <v>351</v>
+        <v>506</v>
+      </c>
+      <c r="B19">
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="1">
+      <c r="A20" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B20">
         <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="B21" t="s">
-        <v>352</v>
+        <v>508</v>
+      </c>
+      <c r="B21">
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" s="1">
-        <v>102</v>
-      </c>
+      <c r="A22" s="1"/>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="B23" t="s">
-        <v>352</v>
+        <v>509</v>
+      </c>
+      <c r="B23">
+        <v>2280</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" s="1">
-        <v>2280</v>
+      <c r="A24" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B24">
+        <v>3978</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B25" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B26" s="62">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="1"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B28" s="1">
+        <v>6458</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="1"/>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="1"/>
+    </row>
+    <row r="33" spans="1:6" ht="16" x14ac:dyDescent="0.4">
+      <c r="A33" s="67" t="s">
+        <v>347</v>
+      </c>
+      <c r="B33" s="67"/>
+      <c r="C33" s="67"/>
+      <c r="D33" s="67"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="66" t="s">
+        <v>348</v>
+      </c>
+      <c r="B34" s="66"/>
+      <c r="C34" s="66"/>
+      <c r="D34" s="66"/>
+      <c r="E34" s="66"/>
+      <c r="F34" s="66"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="66" t="s">
+        <v>349</v>
+      </c>
+      <c r="B35" s="66"/>
+      <c r="C35" s="66"/>
+      <c r="D35" s="66"/>
+      <c r="E35" s="66"/>
+      <c r="F35" s="66"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="66" t="s">
+        <v>350</v>
+      </c>
+      <c r="B36" s="66"/>
+      <c r="C36" s="66"/>
+      <c r="D36" s="66"/>
+      <c r="E36" s="66"/>
+      <c r="F36" s="66"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="66" t="s">
+        <v>351</v>
+      </c>
+      <c r="B37" s="66"/>
+      <c r="C37" s="66"/>
+      <c r="D37" s="66"/>
+      <c r="E37" s="66"/>
+      <c r="F37" s="66"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="66" t="s">
+        <v>352</v>
+      </c>
+      <c r="B38" s="66"/>
+      <c r="C38" s="66"/>
+      <c r="D38" s="66"/>
+      <c r="E38" s="66"/>
+      <c r="F38" s="66"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="66" t="s">
         <v>353</v>
       </c>
-      <c r="B25" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" s="1">
-        <v>4106</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
+      <c r="B39" s="66"/>
+      <c r="C39" s="66"/>
+      <c r="D39" s="66"/>
+      <c r="E39" s="66"/>
+      <c r="F39" s="66"/>
+    </row>
+    <row r="42" spans="1:6" ht="16" x14ac:dyDescent="0.4">
+      <c r="A42" s="67" t="s">
         <v>354</v>
       </c>
-      <c r="B27" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" s="1">
-        <v>1826</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="B29" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" s="1">
-        <v>8</v>
-      </c>
-      <c r="B30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="16" x14ac:dyDescent="0.4">
-      <c r="A33" s="74" t="s">
-        <v>358</v>
-      </c>
-      <c r="B33" s="74"/>
-      <c r="C33" s="74"/>
-      <c r="D33" s="74"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="73" t="s">
-        <v>359</v>
-      </c>
-      <c r="B34" s="73"/>
-      <c r="C34" s="73"/>
-      <c r="D34" s="73"/>
-      <c r="E34" s="73"/>
-      <c r="F34" s="73"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="73" t="s">
-        <v>360</v>
-      </c>
-      <c r="B35" s="73"/>
-      <c r="C35" s="73"/>
-      <c r="D35" s="73"/>
-      <c r="E35" s="73"/>
-      <c r="F35" s="73"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="73" t="s">
-        <v>361</v>
-      </c>
-      <c r="B36" s="73"/>
-      <c r="C36" s="73"/>
-      <c r="D36" s="73"/>
-      <c r="E36" s="73"/>
-      <c r="F36" s="73"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="73" t="s">
-        <v>362</v>
-      </c>
-      <c r="B37" s="73"/>
-      <c r="C37" s="73"/>
-      <c r="D37" s="73"/>
-      <c r="E37" s="73"/>
-      <c r="F37" s="73"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="73" t="s">
-        <v>363</v>
-      </c>
-      <c r="B38" s="73"/>
-      <c r="C38" s="73"/>
-      <c r="D38" s="73"/>
-      <c r="E38" s="73"/>
-      <c r="F38" s="73"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="73" t="s">
-        <v>364</v>
-      </c>
-      <c r="B39" s="73"/>
-      <c r="C39" s="73"/>
-      <c r="D39" s="73"/>
-      <c r="E39" s="73"/>
-      <c r="F39" s="73"/>
-    </row>
-    <row r="42" spans="1:6" ht="16" x14ac:dyDescent="0.4">
-      <c r="A42" s="74" t="s">
-        <v>365</v>
-      </c>
-      <c r="B42" s="74"/>
-      <c r="C42" s="74"/>
-      <c r="D42" s="74"/>
+      <c r="B42" s="67"/>
+      <c r="C42" s="67"/>
+      <c r="D42" s="67"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="44" t="s">
@@ -5937,13 +5902,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A39:F39"/>
     <mergeCell ref="A42:D42"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A16:D16"/>
     <mergeCell ref="A33:D33"/>
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="A35:F35"/>
@@ -5954,1479 +5918,1502 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{091ED868-C890-44F2-A835-FA85CEA4285D}">
-  <dimension ref="A1:G62"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C17668D2-9453-40AD-9562-24E135DC66FA}">
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="40.6328125" customWidth="1"/>
+    <col min="1" max="1" width="42.6328125" customWidth="1"/>
     <col min="2" max="2" width="18.6328125" customWidth="1"/>
     <col min="3" max="3" width="20.6328125" customWidth="1"/>
-    <col min="4" max="4" width="55.6328125" style="31" customWidth="1"/>
-    <col min="5" max="5" width="50.6328125" style="31" customWidth="1"/>
-    <col min="6" max="6" width="20.6328125" style="31" customWidth="1"/>
+    <col min="4" max="4" width="40.54296875" style="31" customWidth="1"/>
+    <col min="5" max="5" width="23.1796875" style="31" customWidth="1"/>
+    <col min="6" max="6" width="73.453125" style="31" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="75" t="s">
-        <v>443</v>
-      </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
+      <c r="A1" s="68" t="s">
+        <v>434</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="73" t="s">
-        <v>444</v>
-      </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
+      <c r="A2" s="66" t="s">
+        <v>514</v>
+      </c>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
     </row>
     <row r="4" spans="1:7" ht="16" x14ac:dyDescent="0.4">
-      <c r="A4" s="74" t="s">
-        <v>366</v>
-      </c>
-      <c r="B4" s="74"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
+      <c r="A4" s="67" t="s">
+        <v>355</v>
+      </c>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="34" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>445</v>
+        <v>406</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>446</v>
+        <v>407</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="46" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="B6" s="47">
-        <v>2401</v>
+        <v>2728</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>370</v>
+        <v>520</v>
       </c>
       <c r="D6" s="49">
         <v>2</v>
       </c>
       <c r="E6" s="57" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="F6" s="57" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="46" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="B7" s="47">
-        <v>997</v>
+        <v>1250</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>372</v>
+        <v>522</v>
       </c>
       <c r="D7" s="49">
         <v>1</v>
       </c>
       <c r="E7" s="57" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="F7" s="57" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="46" t="s">
-        <v>330</v>
+        <v>422</v>
       </c>
       <c r="B8" s="47">
-        <v>288</v>
+        <v>180</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>373</v>
+        <v>524</v>
       </c>
       <c r="D8" s="49">
         <v>1</v>
       </c>
       <c r="E8" s="57" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="F8" s="57" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="46" t="s">
-        <v>374</v>
+        <v>423</v>
       </c>
       <c r="B9" s="47">
-        <v>405</v>
+        <v>310</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>375</v>
+        <v>525</v>
       </c>
       <c r="D9" s="49">
         <v>1</v>
       </c>
       <c r="E9" s="57" t="s">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="F9" s="57" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="46" t="s">
-        <v>376</v>
+        <v>330</v>
       </c>
       <c r="B10" s="47">
-        <v>313</v>
+        <v>1200</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>377</v>
+        <v>526</v>
       </c>
       <c r="D10" s="49">
         <v>1</v>
       </c>
       <c r="E10" s="57" t="s">
+        <v>435</v>
+      </c>
+      <c r="F10" s="57" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" s="46" t="s">
+        <v>360</v>
+      </c>
+      <c r="B11" s="47">
+        <v>350</v>
+      </c>
+      <c r="C11" s="47" t="s">
+        <v>527</v>
+      </c>
+      <c r="D11" s="49">
+        <v>1</v>
+      </c>
+      <c r="E11" s="57" t="s">
+        <v>441</v>
+      </c>
+      <c r="F11" s="57" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="46" t="s">
+        <v>361</v>
+      </c>
+      <c r="B12" s="47">
+        <v>440</v>
+      </c>
+      <c r="C12" s="47" t="s">
+        <v>528</v>
+      </c>
+      <c r="D12" s="49">
+        <v>1</v>
+      </c>
+      <c r="E12" s="57" t="s">
+        <v>441</v>
+      </c>
+      <c r="F12" s="57" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="35" t="s">
+        <v>362</v>
+      </c>
+      <c r="B13" s="34">
+        <v>6458</v>
+      </c>
+      <c r="C13" s="43">
+        <v>1</v>
+      </c>
+      <c r="D13" s="2">
+        <v>8</v>
+      </c>
+      <c r="E13" s="58" t="s">
+        <v>515</v>
+      </c>
+      <c r="F13" s="58"/>
+    </row>
+    <row r="16" spans="1:7" ht="16" x14ac:dyDescent="0.4">
+      <c r="A16" s="67" t="s">
+        <v>443</v>
+      </c>
+      <c r="B16" s="67"/>
+      <c r="C16" s="67"/>
+      <c r="D16" s="67"/>
+      <c r="E16" s="67"/>
+      <c r="F16" s="67"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="66" t="s">
+        <v>516</v>
+      </c>
+      <c r="B17" s="66"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="66"/>
+      <c r="E17" s="66"/>
+      <c r="F17" s="66"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="34" t="s">
+        <v>356</v>
+      </c>
+      <c r="B18" s="34" t="s">
+        <v>408</v>
+      </c>
+      <c r="C18" s="34" t="s">
+        <v>409</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="B19" s="3">
+        <v>310</v>
+      </c>
+      <c r="C19" s="3">
+        <v>155</v>
+      </c>
+      <c r="D19" s="50" t="s">
+        <v>425</v>
+      </c>
+      <c r="E19" s="50" t="s">
+        <v>444</v>
+      </c>
+      <c r="F19" s="24" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B20" s="3">
+        <v>350</v>
+      </c>
+      <c r="C20" s="3">
+        <v>32</v>
+      </c>
+      <c r="D20" s="50" t="s">
+        <v>446</v>
+      </c>
+      <c r="E20" s="50" t="s">
+        <v>447</v>
+      </c>
+      <c r="F20" s="24" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="B21" s="3">
+        <v>440</v>
+      </c>
+      <c r="C21" s="3">
+        <v>40</v>
+      </c>
+      <c r="D21" s="50" t="s">
+        <v>446</v>
+      </c>
+      <c r="E21" s="50" t="s">
+        <v>449</v>
+      </c>
+      <c r="F21" s="24" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A22" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="B22" s="9">
+        <v>180</v>
+      </c>
+      <c r="C22" s="9">
+        <v>103</v>
+      </c>
+      <c r="D22" s="52" t="s">
+        <v>451</v>
+      </c>
+      <c r="E22" s="52" t="s">
+        <v>452</v>
+      </c>
+      <c r="F22" s="26" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A23" s="46" t="s">
+        <v>394</v>
+      </c>
+      <c r="B23" s="47">
+        <v>1364</v>
+      </c>
+      <c r="C23" s="47">
+        <v>152</v>
+      </c>
+      <c r="D23" s="49" t="s">
         <v>454</v>
       </c>
-      <c r="F10" s="57" t="s">
+      <c r="E23" s="49" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A11" s="35" t="s">
-        <v>378</v>
-      </c>
-      <c r="B11" s="34">
-        <v>4404</v>
-      </c>
-      <c r="C11" s="43">
+      <c r="F23" s="57" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A24" s="46" t="s">
+        <v>395</v>
+      </c>
+      <c r="B24" s="47">
+        <v>1364</v>
+      </c>
+      <c r="C24" s="47">
+        <v>152</v>
+      </c>
+      <c r="D24" s="49" t="s">
+        <v>454</v>
+      </c>
+      <c r="E24" s="49" t="s">
+        <v>455</v>
+      </c>
+      <c r="F24" s="57" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="46" t="s">
+        <v>366</v>
+      </c>
+      <c r="B25" s="47">
+        <v>1250</v>
+      </c>
+      <c r="C25" s="47">
+        <v>139</v>
+      </c>
+      <c r="D25" s="49" t="s">
+        <v>454</v>
+      </c>
+      <c r="E25" s="49" t="s">
+        <v>455</v>
+      </c>
+      <c r="F25" s="57" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A26" s="46" t="s">
+        <v>330</v>
+      </c>
+      <c r="B26" s="47">
+        <v>1200</v>
+      </c>
+      <c r="C26" s="47">
+        <v>133</v>
+      </c>
+      <c r="D26" s="49" t="s">
+        <v>454</v>
+      </c>
+      <c r="E26" s="49" t="s">
+        <v>456</v>
+      </c>
+      <c r="F26" s="57" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="35" t="s">
+        <v>367</v>
+      </c>
+      <c r="B27" s="34">
+        <v>6458</v>
+      </c>
+      <c r="C27" s="34" t="s">
+        <v>517</v>
+      </c>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="58"/>
+    </row>
+    <row r="29" spans="1:6" ht="16" x14ac:dyDescent="0.4">
+      <c r="A29" s="67" t="s">
+        <v>426</v>
+      </c>
+      <c r="B29" s="67"/>
+      <c r="C29" s="67"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="67"/>
+      <c r="F29" s="67"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="D11" s="2">
-        <v>6</v>
-      </c>
-      <c r="E11" s="58" t="s">
-        <v>456</v>
-      </c>
-      <c r="F11" s="58" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.4">
-      <c r="A14" s="74" t="s">
+      <c r="B30" s="34" t="s">
+        <v>344</v>
+      </c>
+      <c r="C30" s="34" t="s">
+        <v>368</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="B14" s="74"/>
-      <c r="C14" s="74"/>
-      <c r="D14" s="74"/>
-      <c r="E14" s="74"/>
-      <c r="F14" s="74"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="73" t="s">
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31" s="3">
+        <v>10</v>
+      </c>
+      <c r="C31" s="3">
+        <v>162</v>
+      </c>
+      <c r="D31" s="50">
+        <v>200</v>
+      </c>
+      <c r="E31" s="50">
+        <v>362</v>
+      </c>
+      <c r="F31" s="24" t="s">
         <v>459</v>
       </c>
-      <c r="B15" s="73"/>
-      <c r="C15" s="73"/>
-      <c r="D15" s="73"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="73"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="B16" s="34" t="s">
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="6">
+        <v>18</v>
+      </c>
+      <c r="C32" s="6">
+        <v>227</v>
+      </c>
+      <c r="D32" s="51">
+        <v>455</v>
+      </c>
+      <c r="E32" s="51">
+        <v>682</v>
+      </c>
+      <c r="F32" s="25" t="s">
         <v>460</v>
       </c>
-      <c r="C16" s="34" t="s">
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B33" s="9">
+        <v>45</v>
+      </c>
+      <c r="C33" s="9">
+        <v>458</v>
+      </c>
+      <c r="D33" s="52">
+        <v>1125</v>
+      </c>
+      <c r="E33" s="52">
+        <v>1583</v>
+      </c>
+      <c r="F33" s="26" t="s">
         <v>461</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="E16" s="2" t="s">
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="B34" s="12">
+        <v>10</v>
+      </c>
+      <c r="C34" s="12">
+        <v>38</v>
+      </c>
+      <c r="D34" s="53">
+        <v>343</v>
+      </c>
+      <c r="E34" s="53">
+        <v>381</v>
+      </c>
+      <c r="F34" s="27" t="s">
         <v>462</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="46" t="s">
-        <v>412</v>
-      </c>
-      <c r="B17" s="47">
-        <v>1201</v>
-      </c>
-      <c r="C17" s="47">
-        <v>155</v>
-      </c>
-      <c r="D17" s="49" t="s">
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="B35" s="15">
+        <v>8</v>
+      </c>
+      <c r="C35" s="15">
+        <v>80</v>
+      </c>
+      <c r="D35" s="54">
+        <v>187</v>
+      </c>
+      <c r="E35" s="54">
+        <v>267</v>
+      </c>
+      <c r="F35" s="28" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="B36" s="18">
+        <v>4</v>
+      </c>
+      <c r="C36" s="18">
+        <v>51</v>
+      </c>
+      <c r="D36" s="55">
+        <v>80</v>
+      </c>
+      <c r="E36" s="55">
+        <v>131</v>
+      </c>
+      <c r="F36" s="29" t="s">
         <v>463</v>
       </c>
-      <c r="E17" s="70">
-        <v>0.86</v>
-      </c>
-      <c r="F17" s="57" t="s">
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="22" t="s">
+        <v>313</v>
+      </c>
+      <c r="B37" s="21">
+        <v>7</v>
+      </c>
+      <c r="C37" s="21">
+        <v>234</v>
+      </c>
+      <c r="D37" s="56">
+        <v>338</v>
+      </c>
+      <c r="E37" s="56">
+        <v>572</v>
+      </c>
+      <c r="F37" s="30" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="35" t="s">
+        <v>346</v>
+      </c>
+      <c r="B38" s="34">
+        <v>102</v>
+      </c>
+      <c r="C38" s="34">
+        <v>1250</v>
+      </c>
+      <c r="D38" s="2">
+        <v>2728</v>
+      </c>
+      <c r="E38" s="2">
+        <v>3978</v>
+      </c>
+      <c r="F38" s="58"/>
+    </row>
+    <row r="40" spans="1:6" ht="16" x14ac:dyDescent="0.4">
+      <c r="A40" s="67" t="s">
         <v>464</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="87" x14ac:dyDescent="0.35">
-      <c r="A18" s="46" t="s">
-        <v>413</v>
-      </c>
-      <c r="B18" s="47">
-        <v>1200</v>
-      </c>
-      <c r="C18" s="47">
-        <v>155</v>
-      </c>
-      <c r="D18" s="49" t="s">
-        <v>463</v>
-      </c>
-      <c r="E18" s="70">
-        <v>0.86</v>
-      </c>
-      <c r="F18" s="57" t="s">
+      <c r="B40" s="67"/>
+      <c r="C40" s="67"/>
+      <c r="D40" s="67"/>
+      <c r="E40" s="67"/>
+      <c r="F40" s="67"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="34" t="s">
+        <v>371</v>
+      </c>
+      <c r="B41" s="34" t="s">
+        <v>372</v>
+      </c>
+      <c r="C41" s="34" t="s">
+        <v>374</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="46" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="46" t="s">
-        <v>382</v>
-      </c>
-      <c r="B19" s="47">
-        <v>997</v>
-      </c>
-      <c r="C19" s="47">
-        <v>155</v>
-      </c>
-      <c r="D19" s="49" t="s">
-        <v>463</v>
-      </c>
-      <c r="E19" s="70">
-        <v>0.71</v>
-      </c>
-      <c r="F19" s="57" t="s">
+      <c r="B42" s="46" t="s">
+        <v>427</v>
+      </c>
+      <c r="C42" s="47">
+        <v>500</v>
+      </c>
+      <c r="D42" s="57" t="s">
         <v>466</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A20" s="46" t="s">
-        <v>330</v>
-      </c>
-      <c r="B20" s="47">
-        <v>288</v>
-      </c>
-      <c r="C20" s="47">
-        <v>48</v>
-      </c>
-      <c r="D20" s="49" t="s">
+      <c r="E42" s="57" t="s">
         <v>467</v>
-      </c>
-      <c r="E20" s="49" t="s">
-        <v>468</v>
-      </c>
-      <c r="F20" s="57" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="46" t="s">
-        <v>374</v>
-      </c>
-      <c r="B21" s="47">
-        <v>405</v>
-      </c>
-      <c r="C21" s="47">
-        <v>45</v>
-      </c>
-      <c r="D21" s="49" t="s">
-        <v>463</v>
-      </c>
-      <c r="E21" s="49" t="s">
-        <v>470</v>
-      </c>
-      <c r="F21" s="57" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="46" t="s">
-        <v>376</v>
-      </c>
-      <c r="B22" s="47">
-        <v>313</v>
-      </c>
-      <c r="C22" s="47">
-        <v>35</v>
-      </c>
-      <c r="D22" s="49" t="s">
-        <v>463</v>
-      </c>
-      <c r="E22" s="49" t="s">
-        <v>472</v>
-      </c>
-      <c r="F22" s="57" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="35" t="s">
-        <v>383</v>
-      </c>
-      <c r="B23" s="34">
-        <v>4404</v>
-      </c>
-      <c r="C23" s="34" t="s">
-        <v>474</v>
-      </c>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="58"/>
-    </row>
-    <row r="25" spans="1:6" ht="16" x14ac:dyDescent="0.4">
-      <c r="A25" s="74" t="s">
-        <v>419</v>
-      </c>
-      <c r="B25" s="74"/>
-      <c r="C25" s="74"/>
-      <c r="D25" s="74"/>
-      <c r="E25" s="74"/>
-      <c r="F25" s="74"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="B26" s="34" t="s">
-        <v>346</v>
-      </c>
-      <c r="C26" s="34" t="s">
-        <v>384</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B27" s="3">
-        <v>10</v>
-      </c>
-      <c r="C27" s="3">
-        <v>154</v>
-      </c>
-      <c r="D27" s="50">
-        <v>189</v>
-      </c>
-      <c r="E27" s="50">
-        <v>343</v>
-      </c>
-      <c r="F27" s="24" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="6">
-        <v>18</v>
-      </c>
-      <c r="C28" s="6">
-        <v>198</v>
-      </c>
-      <c r="D28" s="51">
-        <v>412</v>
-      </c>
-      <c r="E28" s="51">
-        <v>610</v>
-      </c>
-      <c r="F28" s="25" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="B29" s="9">
-        <v>45</v>
-      </c>
-      <c r="C29" s="9">
-        <v>420</v>
-      </c>
-      <c r="D29" s="52">
-        <v>1044</v>
-      </c>
-      <c r="E29" s="52">
-        <v>1464</v>
-      </c>
-      <c r="F29" s="26" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="B30" s="12">
-        <v>10</v>
-      </c>
-      <c r="C30" s="12">
-        <v>36</v>
-      </c>
-      <c r="D30" s="53">
-        <v>341</v>
-      </c>
-      <c r="E30" s="53">
-        <v>377</v>
-      </c>
-      <c r="F30" s="27" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="16" t="s">
-        <v>277</v>
-      </c>
-      <c r="B31" s="15">
-        <v>8</v>
-      </c>
-      <c r="C31" s="15">
-        <v>72</v>
-      </c>
-      <c r="D31" s="54">
-        <v>171</v>
-      </c>
-      <c r="E31" s="54">
-        <v>243</v>
-      </c>
-      <c r="F31" s="28" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="19" t="s">
-        <v>299</v>
-      </c>
-      <c r="B32" s="18">
-        <v>4</v>
-      </c>
-      <c r="C32" s="18">
-        <v>49</v>
-      </c>
-      <c r="D32" s="55">
-        <v>72</v>
-      </c>
-      <c r="E32" s="55">
-        <v>121</v>
-      </c>
-      <c r="F32" s="29" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="22" t="s">
-        <v>313</v>
-      </c>
-      <c r="B33" s="21">
-        <v>7</v>
-      </c>
-      <c r="C33" s="21">
-        <v>212</v>
-      </c>
-      <c r="D33" s="56">
-        <v>316</v>
-      </c>
-      <c r="E33" s="56">
-        <v>528</v>
-      </c>
-      <c r="F33" s="30" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="35" t="s">
-        <v>348</v>
-      </c>
-      <c r="B34" s="34">
-        <v>102</v>
-      </c>
-      <c r="C34" s="34">
-        <v>1141</v>
-      </c>
-      <c r="D34" s="2">
-        <v>2545</v>
-      </c>
-      <c r="E34" s="2">
-        <v>3686</v>
-      </c>
-      <c r="F34" s="58"/>
-    </row>
-    <row r="36" spans="1:6" ht="16" x14ac:dyDescent="0.4">
-      <c r="A36" s="74" t="s">
-        <v>426</v>
-      </c>
-      <c r="B36" s="74"/>
-      <c r="C36" s="74"/>
-      <c r="D36" s="74"/>
-      <c r="E36" s="74"/>
-      <c r="F36" s="74"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="34" t="s">
-        <v>387</v>
-      </c>
-      <c r="B37" s="34" t="s">
-        <v>388</v>
-      </c>
-      <c r="C37" s="34" t="s">
-        <v>390</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A38" s="46" t="s">
-        <v>392</v>
-      </c>
-      <c r="B38" s="46" t="s">
-        <v>402</v>
-      </c>
-      <c r="C38" s="47">
-        <v>280</v>
-      </c>
-      <c r="D38" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="E38" s="57" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A39" s="46" t="s">
-        <v>394</v>
-      </c>
-      <c r="B39" s="46" t="s">
-        <v>427</v>
-      </c>
-      <c r="C39" s="47">
-        <v>953</v>
-      </c>
-      <c r="D39" s="57" t="s">
-        <v>428</v>
-      </c>
-      <c r="E39" s="57" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A40" s="46" t="s">
-        <v>395</v>
-      </c>
-      <c r="B40" s="46" t="s">
-        <v>429</v>
-      </c>
-      <c r="C40" s="47">
-        <v>1464</v>
-      </c>
-      <c r="D40" s="57" t="s">
-        <v>396</v>
-      </c>
-      <c r="E40" s="57" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A41" s="46" t="s">
-        <v>397</v>
-      </c>
-      <c r="B41" s="46" t="s">
-        <v>430</v>
-      </c>
-      <c r="C41" s="47">
-        <v>620</v>
-      </c>
-      <c r="D41" s="57" t="s">
-        <v>398</v>
-      </c>
-      <c r="E41" s="57" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A42" s="46" t="s">
-        <v>431</v>
-      </c>
-      <c r="B42" s="46" t="s">
-        <v>432</v>
-      </c>
-      <c r="C42" s="47">
-        <v>649</v>
-      </c>
-      <c r="D42" s="57" t="s">
-        <v>399</v>
-      </c>
-      <c r="E42" s="57" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A43" s="46" t="s">
-        <v>433</v>
+        <v>468</v>
       </c>
       <c r="B43" s="46" t="s">
-        <v>434</v>
+        <v>386</v>
       </c>
       <c r="C43" s="47">
-        <v>288</v>
+        <v>610</v>
       </c>
       <c r="D43" s="57" t="s">
-        <v>435</v>
+        <v>469</v>
       </c>
       <c r="E43" s="57" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A44" s="46" t="s">
+        <v>376</v>
+      </c>
+      <c r="B44" s="46" t="s">
+        <v>471</v>
+      </c>
+      <c r="C44" s="47">
+        <v>1044</v>
+      </c>
+      <c r="D44" s="57" t="s">
+        <v>428</v>
+      </c>
+      <c r="E44" s="57" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A45" s="46" t="s">
+        <v>377</v>
+      </c>
+      <c r="B45" s="46" t="s">
+        <v>473</v>
+      </c>
+      <c r="C45" s="47">
+        <v>1583</v>
+      </c>
+      <c r="D45" s="57" t="s">
+        <v>378</v>
+      </c>
+      <c r="E45" s="57" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A46" s="46" t="s">
+        <v>379</v>
+      </c>
+      <c r="B46" s="46" t="s">
+        <v>401</v>
+      </c>
+      <c r="C46" s="47">
+        <v>648</v>
+      </c>
+      <c r="D46" s="57" t="s">
+        <v>380</v>
+      </c>
+      <c r="E46" s="57" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A47" s="46" t="s">
+        <v>399</v>
+      </c>
+      <c r="B47" s="46" t="s">
+        <v>474</v>
+      </c>
+      <c r="C47" s="47">
+        <v>703</v>
+      </c>
+      <c r="D47" s="57" t="s">
+        <v>381</v>
+      </c>
+      <c r="E47" s="57" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A48" s="46" t="s">
+        <v>400</v>
+      </c>
+      <c r="B48" s="46" t="s">
+        <v>475</v>
+      </c>
+      <c r="C48" s="47">
+        <v>488</v>
+      </c>
+      <c r="D48" s="57" t="s">
+        <v>429</v>
+      </c>
+      <c r="E48" s="57" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A51" s="67" t="s">
+        <v>431</v>
+      </c>
+      <c r="B51" s="67"/>
+      <c r="C51" s="67"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" s="35" t="s">
+        <v>382</v>
+      </c>
+      <c r="B52" s="35" t="s">
+        <v>412</v>
+      </c>
+      <c r="C52" s="35" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="48" t="s">
+        <v>413</v>
+      </c>
+      <c r="B53" s="48" t="s">
+        <v>476</v>
+      </c>
+      <c r="C53" s="48" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" s="46" t="s">
+        <v>414</v>
+      </c>
+      <c r="B54" s="46" t="s">
         <v>478</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" ht="16" x14ac:dyDescent="0.4">
-      <c r="A46" s="74" t="s">
+      <c r="C54" s="46" t="s">
         <v>479</v>
       </c>
-      <c r="B46" s="74"/>
-      <c r="C46" s="74"/>
-      <c r="D46" s="74"/>
-      <c r="E46" s="74"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="B47" s="34" t="s">
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" s="48" t="s">
         <v>480</v>
       </c>
-      <c r="C47" s="34" t="s">
+      <c r="B55" s="48" t="s">
         <v>481</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="C55" s="48" t="s">
         <v>482</v>
       </c>
-      <c r="E47" s="2" t="s">
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" s="46" t="s">
+        <v>415</v>
+      </c>
+      <c r="B56" s="46" t="s">
+        <v>416</v>
+      </c>
+      <c r="C56" s="46" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" s="48" t="s">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" s="48" t="s">
+        <v>402</v>
+      </c>
+      <c r="B57" s="48" t="s">
+        <v>417</v>
+      </c>
+      <c r="C57" s="48" t="s">
         <v>484</v>
       </c>
-      <c r="B48" s="69">
-        <v>2790</v>
-      </c>
-      <c r="C48" s="69">
-        <v>2401</v>
-      </c>
-      <c r="D48" s="71">
-        <v>389</v>
-      </c>
-      <c r="E48" s="72" t="s">
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" s="46" t="s">
+        <v>418</v>
+      </c>
+      <c r="B58" s="46" t="s">
+        <v>432</v>
+      </c>
+      <c r="C58" s="46" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A49" s="46" t="s">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" s="48" t="s">
         <v>486</v>
       </c>
-      <c r="B49" s="47">
-        <v>1395</v>
-      </c>
-      <c r="C49" s="47">
-        <v>997</v>
-      </c>
-      <c r="D49" s="49">
-        <v>398</v>
-      </c>
-      <c r="E49" s="57" t="s">
+      <c r="B59" s="48" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A50" s="48" t="s">
+      <c r="C59" s="48" t="s">
         <v>488</v>
       </c>
-      <c r="B50" s="69">
-        <v>930</v>
-      </c>
-      <c r="C50" s="69">
-        <v>288</v>
-      </c>
-      <c r="D50" s="71">
-        <v>642</v>
-      </c>
-      <c r="E50" s="72" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A51" s="46" t="s">
-        <v>490</v>
-      </c>
-      <c r="B51" s="47">
-        <v>405</v>
-      </c>
-      <c r="C51" s="47">
-        <v>405</v>
-      </c>
-      <c r="D51" s="49">
-        <v>0</v>
-      </c>
-      <c r="E51" s="57" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A52" s="48" t="s">
-        <v>492</v>
-      </c>
-      <c r="B52" s="69">
-        <v>313</v>
-      </c>
-      <c r="C52" s="69">
-        <v>313</v>
-      </c>
-      <c r="D52" s="71">
-        <v>0</v>
-      </c>
-      <c r="E52" s="72" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="16" x14ac:dyDescent="0.4">
-      <c r="A55" s="74" t="s">
-        <v>436</v>
-      </c>
-      <c r="B55" s="74"/>
-      <c r="C55" s="74"/>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A56" s="35" t="s">
-        <v>400</v>
-      </c>
-      <c r="B56" s="35" t="s">
-        <v>494</v>
-      </c>
-      <c r="C56" s="35" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A57" s="48" t="s">
-        <v>495</v>
-      </c>
-      <c r="B57" s="48" t="s">
-        <v>496</v>
-      </c>
-      <c r="C57" s="48" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A58" s="46" t="s">
-        <v>498</v>
-      </c>
-      <c r="B58" s="46" t="s">
-        <v>499</v>
-      </c>
-      <c r="C58" s="46" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A59" s="48" t="s">
-        <v>501</v>
-      </c>
-      <c r="B59" s="48" t="s">
-        <v>502</v>
-      </c>
-      <c r="C59" s="48" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A60" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="B60" s="46" t="s">
-        <v>504</v>
-      </c>
-      <c r="C60" s="46" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A61" s="48" t="s">
-        <v>506</v>
-      </c>
-      <c r="B61" s="48" t="s">
-        <v>507</v>
-      </c>
-      <c r="C61" s="48" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A62" s="46" t="s">
-        <v>509</v>
-      </c>
-      <c r="B62" s="46" t="s">
-        <v>510</v>
-      </c>
-      <c r="C62" s="46" t="s">
-        <v>511</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A55:C55"/>
+  <mergeCells count="8">
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A51:C51"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A29:F29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6E5C2AE-6B9B-4D93-948A-F0008F203D72}">
-  <dimension ref="A1:L23"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8883BF8-3712-4B52-8271-E3AA297B7ED1}">
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.6328125" customWidth="1"/>
-    <col min="2" max="2" width="2.6328125" customWidth="1"/>
-    <col min="3" max="11" width="10.6328125" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" customWidth="1"/>
+    <col min="2" max="2" width="3.6328125" customWidth="1"/>
+    <col min="3" max="13" width="8.6328125" customWidth="1"/>
+    <col min="14" max="14" width="10.6328125" customWidth="1"/>
+    <col min="15" max="15" width="8.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="75" t="s">
-        <v>512</v>
-      </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="73" t="s">
-        <v>513</v>
-      </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="78" t="s">
-        <v>514</v>
-      </c>
-      <c r="B4" s="78"/>
-      <c r="C4" s="34" t="s">
-        <v>402</v>
-      </c>
-      <c r="D4" s="34" t="s">
+    <row r="1" spans="1:15" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="68" t="s">
+        <v>492</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="66"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A2" s="69" t="s">
+        <v>493</v>
+      </c>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+      <c r="O2" s="66"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4" s="61" t="s">
+        <v>494</v>
+      </c>
+      <c r="B4" s="61"/>
+      <c r="C4" s="61" t="s">
+        <v>384</v>
+      </c>
+      <c r="D4" s="61" t="s">
+        <v>385</v>
+      </c>
+      <c r="E4" s="61" t="s">
+        <v>386</v>
+      </c>
+      <c r="F4" s="61" t="s">
+        <v>387</v>
+      </c>
+      <c r="G4" s="61" t="s">
+        <v>388</v>
+      </c>
+      <c r="H4" s="61" t="s">
+        <v>389</v>
+      </c>
+      <c r="I4" s="61" t="s">
+        <v>390</v>
+      </c>
+      <c r="J4" s="61" t="s">
+        <v>391</v>
+      </c>
+      <c r="K4" s="61" t="s">
+        <v>392</v>
+      </c>
+      <c r="L4" s="61" t="s">
+        <v>489</v>
+      </c>
+      <c r="M4" s="61" t="s">
+        <v>490</v>
+      </c>
+      <c r="N4" s="61" t="s">
+        <v>393</v>
+      </c>
+      <c r="O4" s="61" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>496</v>
+      </c>
+      <c r="C5" s="64">
+        <v>155</v>
+      </c>
+      <c r="D5" s="64">
+        <v>155</v>
+      </c>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
+      <c r="K5" s="64"/>
+      <c r="L5" s="64"/>
+      <c r="M5" s="64"/>
+      <c r="N5" s="64">
+        <f>SUM(C5:M5)</f>
+        <v>310</v>
+      </c>
+      <c r="O5" s="65">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>360</v>
+      </c>
+      <c r="C6" s="64">
+        <v>35</v>
+      </c>
+      <c r="D6" s="64">
+        <v>35</v>
+      </c>
+      <c r="E6" s="64">
+        <v>30</v>
+      </c>
+      <c r="F6" s="64">
+        <v>30</v>
+      </c>
+      <c r="G6" s="64">
+        <v>30</v>
+      </c>
+      <c r="H6" s="64">
+        <v>30</v>
+      </c>
+      <c r="I6" s="64">
+        <v>30</v>
+      </c>
+      <c r="J6" s="64">
+        <v>30</v>
+      </c>
+      <c r="K6" s="64">
+        <v>30</v>
+      </c>
+      <c r="L6" s="64">
+        <v>35</v>
+      </c>
+      <c r="M6" s="64">
+        <v>35</v>
+      </c>
+      <c r="N6" s="64">
+        <f>SUM(C6:M6)</f>
+        <v>350</v>
+      </c>
+      <c r="O6" s="65">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>361</v>
+      </c>
+      <c r="C7" s="64">
+        <v>40</v>
+      </c>
+      <c r="D7" s="64">
+        <v>40</v>
+      </c>
+      <c r="E7" s="64">
+        <v>40</v>
+      </c>
+      <c r="F7" s="64">
+        <v>40</v>
+      </c>
+      <c r="G7" s="64">
+        <v>40</v>
+      </c>
+      <c r="H7" s="64">
+        <v>40</v>
+      </c>
+      <c r="I7" s="64">
+        <v>40</v>
+      </c>
+      <c r="J7" s="64">
+        <v>40</v>
+      </c>
+      <c r="K7" s="64">
+        <v>40</v>
+      </c>
+      <c r="L7" s="64">
+        <v>40</v>
+      </c>
+      <c r="M7" s="64">
+        <v>40</v>
+      </c>
+      <c r="N7" s="64">
+        <f>SUM(C7:M7)</f>
+        <v>440</v>
+      </c>
+      <c r="O7" s="65">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>422</v>
+      </c>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64">
+        <v>90</v>
+      </c>
+      <c r="F8" s="64">
+        <v>90</v>
+      </c>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="64"/>
+      <c r="K8" s="64"/>
+      <c r="L8" s="64"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="64">
+        <f>SUM(C8:M8)</f>
+        <v>180</v>
+      </c>
+      <c r="O8" s="65">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>419</v>
+      </c>
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64">
+        <v>130</v>
+      </c>
+      <c r="F9" s="64">
+        <v>155</v>
+      </c>
+      <c r="G9" s="64">
+        <v>155</v>
+      </c>
+      <c r="H9" s="64">
+        <v>155</v>
+      </c>
+      <c r="I9" s="64">
+        <v>155</v>
+      </c>
+      <c r="J9" s="64">
+        <v>155</v>
+      </c>
+      <c r="K9" s="64">
+        <v>155</v>
+      </c>
+      <c r="L9" s="64">
+        <v>155</v>
+      </c>
+      <c r="M9" s="64">
+        <v>149</v>
+      </c>
+      <c r="N9" s="64">
+        <f>SUM(C9:M9)</f>
+        <v>1364</v>
+      </c>
+      <c r="O9" s="65">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>420</v>
+      </c>
+      <c r="C10" s="64"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64">
+        <v>130</v>
+      </c>
+      <c r="F10" s="64">
+        <v>155</v>
+      </c>
+      <c r="G10" s="64">
+        <v>155</v>
+      </c>
+      <c r="H10" s="64">
+        <v>155</v>
+      </c>
+      <c r="I10" s="64">
+        <v>155</v>
+      </c>
+      <c r="J10" s="64">
+        <v>155</v>
+      </c>
+      <c r="K10" s="64">
+        <v>155</v>
+      </c>
+      <c r="L10" s="64">
+        <v>155</v>
+      </c>
+      <c r="M10" s="64">
+        <v>149</v>
+      </c>
+      <c r="N10" s="64">
+        <f>SUM(C10:M10)</f>
+        <v>1364</v>
+      </c>
+      <c r="O10" s="65">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>421</v>
+      </c>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64">
+        <v>110</v>
+      </c>
+      <c r="F11" s="64">
+        <v>140</v>
+      </c>
+      <c r="G11" s="64">
+        <v>145</v>
+      </c>
+      <c r="H11" s="64">
+        <v>145</v>
+      </c>
+      <c r="I11" s="64">
+        <v>145</v>
+      </c>
+      <c r="J11" s="64">
+        <v>145</v>
+      </c>
+      <c r="K11" s="64">
+        <v>145</v>
+      </c>
+      <c r="L11" s="64">
+        <v>145</v>
+      </c>
+      <c r="M11" s="64">
+        <v>130</v>
+      </c>
+      <c r="N11" s="64">
+        <f>SUM(C11:M11)</f>
+        <v>1250</v>
+      </c>
+      <c r="O11" s="65">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>433</v>
+      </c>
+      <c r="C12" s="64"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64">
+        <v>80</v>
+      </c>
+      <c r="F12" s="64">
+        <v>120</v>
+      </c>
+      <c r="G12" s="64">
+        <v>150</v>
+      </c>
+      <c r="H12" s="64">
+        <v>155</v>
+      </c>
+      <c r="I12" s="64">
+        <v>155</v>
+      </c>
+      <c r="J12" s="64">
+        <v>155</v>
+      </c>
+      <c r="K12" s="64">
+        <v>145</v>
+      </c>
+      <c r="L12" s="64">
+        <v>130</v>
+      </c>
+      <c r="M12" s="64">
+        <v>110</v>
+      </c>
+      <c r="N12" s="64">
+        <f>SUM(C12:M12)</f>
+        <v>1200</v>
+      </c>
+      <c r="O12" s="65">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A13" s="60" t="s">
+        <v>497</v>
+      </c>
+      <c r="C13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="64"/>
+      <c r="J13" s="64"/>
+      <c r="K13" s="64"/>
+      <c r="L13" s="64"/>
+      <c r="M13" s="64"/>
+      <c r="N13" s="64"/>
+      <c r="O13" s="64"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C14" s="64">
+        <f>SUM(C5:C12)</f>
+        <v>230</v>
+      </c>
+      <c r="D14" s="64">
+        <f>SUM(D5:D12)</f>
+        <v>230</v>
+      </c>
+      <c r="E14" s="64">
+        <f>SUM(E5:E12)</f>
+        <v>610</v>
+      </c>
+      <c r="F14" s="64">
+        <f>SUM(F5:F12)</f>
+        <v>730</v>
+      </c>
+      <c r="G14" s="64">
+        <f>SUM(G5:G12)</f>
+        <v>675</v>
+      </c>
+      <c r="H14" s="64">
+        <f>SUM(H5:H12)</f>
+        <v>680</v>
+      </c>
+      <c r="I14" s="64">
+        <f>SUM(I5:I12)</f>
+        <v>680</v>
+      </c>
+      <c r="J14" s="64">
+        <f>SUM(J5:J12)</f>
+        <v>680</v>
+      </c>
+      <c r="K14" s="64">
+        <f>SUM(K5:K12)</f>
+        <v>670</v>
+      </c>
+      <c r="L14" s="64">
+        <f>SUM(L5:L12)</f>
+        <v>660</v>
+      </c>
+      <c r="M14" s="64">
+        <f>SUM(M5:M12)</f>
+        <v>613</v>
+      </c>
+      <c r="N14" s="64">
+        <f>SUM(N5:N12)</f>
+        <v>6458</v>
+      </c>
+      <c r="O14" s="64"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>397</v>
+      </c>
+      <c r="C15" s="64">
+        <v>3</v>
+      </c>
+      <c r="D15" s="64">
+        <v>3</v>
+      </c>
+      <c r="E15" s="64">
+        <v>7</v>
+      </c>
+      <c r="F15" s="64">
+        <v>7</v>
+      </c>
+      <c r="G15" s="64">
+        <v>6</v>
+      </c>
+      <c r="H15" s="64">
+        <v>6</v>
+      </c>
+      <c r="I15" s="64">
+        <v>6</v>
+      </c>
+      <c r="J15" s="64">
+        <v>6</v>
+      </c>
+      <c r="K15" s="64">
+        <v>6</v>
+      </c>
+      <c r="L15" s="64">
+        <v>6</v>
+      </c>
+      <c r="M15" s="64">
+        <v>6</v>
+      </c>
+      <c r="N15" s="64"/>
+      <c r="O15" s="64"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>371</v>
+      </c>
+      <c r="C19" t="s">
+        <v>384</v>
+      </c>
+      <c r="D19" t="s">
+        <v>385</v>
+      </c>
+      <c r="E19" t="s">
+        <v>386</v>
+      </c>
+      <c r="F19" t="s">
+        <v>387</v>
+      </c>
+      <c r="G19" t="s">
+        <v>388</v>
+      </c>
+      <c r="H19" t="s">
+        <v>389</v>
+      </c>
+      <c r="I19" t="s">
+        <v>390</v>
+      </c>
+      <c r="J19" t="s">
+        <v>391</v>
+      </c>
+      <c r="K19" t="s">
+        <v>392</v>
+      </c>
+      <c r="L19" t="s">
+        <v>489</v>
+      </c>
+      <c r="M19" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>498</v>
+      </c>
+      <c r="C20" s="63"/>
+      <c r="D20" s="63"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>499</v>
+      </c>
+      <c r="E21" s="63"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>500</v>
+      </c>
+      <c r="F22" s="63"/>
+      <c r="G22" s="63"/>
+      <c r="H22" s="63"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>501</v>
+      </c>
+      <c r="G23" s="63"/>
+      <c r="H23" s="63"/>
+      <c r="I23" s="63"/>
+      <c r="J23" s="63"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>403</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="I24" s="63"/>
+      <c r="J24" s="63"/>
+      <c r="K24" s="63"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>404</v>
       </c>
-      <c r="F4" s="34" t="s">
+      <c r="J25" s="63"/>
+      <c r="K25" s="63"/>
+      <c r="L25" s="63"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>405</v>
       </c>
-      <c r="G4" s="34" t="s">
-        <v>406</v>
-      </c>
-      <c r="H4" s="34" t="s">
-        <v>407</v>
-      </c>
-      <c r="I4" s="34" t="s">
-        <v>408</v>
-      </c>
-      <c r="J4" s="34" t="s">
-        <v>409</v>
-      </c>
-      <c r="K4" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="L4" s="34" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="76" t="s">
-        <v>515</v>
-      </c>
-      <c r="B5" s="77"/>
-      <c r="C5" s="62">
-        <v>120</v>
-      </c>
-      <c r="D5" s="62">
-        <v>155</v>
-      </c>
-      <c r="E5" s="62">
-        <v>155</v>
-      </c>
-      <c r="F5" s="62">
-        <v>155</v>
-      </c>
-      <c r="G5" s="62">
-        <v>155</v>
-      </c>
-      <c r="H5" s="62">
-        <v>155</v>
-      </c>
-      <c r="I5" s="62">
-        <v>155</v>
-      </c>
-      <c r="J5" s="62">
-        <v>100</v>
-      </c>
-      <c r="K5" s="62">
-        <v>51</v>
-      </c>
-      <c r="L5" s="60">
-        <v>1201</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A6" s="76" t="s">
-        <v>516</v>
-      </c>
-      <c r="B6" s="77"/>
-      <c r="C6" s="63">
-        <v>120</v>
-      </c>
-      <c r="D6" s="63">
-        <v>155</v>
-      </c>
-      <c r="E6" s="63">
-        <v>155</v>
-      </c>
-      <c r="F6" s="63">
-        <v>155</v>
-      </c>
-      <c r="G6" s="63">
-        <v>155</v>
-      </c>
-      <c r="H6" s="63">
-        <v>155</v>
-      </c>
-      <c r="I6" s="63">
-        <v>155</v>
-      </c>
-      <c r="J6" s="63">
-        <v>100</v>
-      </c>
-      <c r="K6" s="63">
-        <v>50</v>
-      </c>
-      <c r="L6" s="60">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7" s="76" t="s">
-        <v>517</v>
-      </c>
-      <c r="B7" s="77"/>
-      <c r="C7" s="64">
-        <v>60</v>
-      </c>
-      <c r="D7" s="64">
-        <v>140</v>
-      </c>
-      <c r="E7" s="64">
-        <v>155</v>
-      </c>
-      <c r="F7" s="64">
-        <v>155</v>
-      </c>
-      <c r="G7" s="64">
-        <v>155</v>
-      </c>
-      <c r="H7" s="64">
-        <v>140</v>
-      </c>
-      <c r="I7" s="64">
-        <v>110</v>
-      </c>
-      <c r="J7" s="64">
-        <v>60</v>
-      </c>
-      <c r="K7" s="64">
-        <v>22</v>
-      </c>
-      <c r="L7" s="60">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A8" s="76" t="s">
-        <v>518</v>
-      </c>
-      <c r="B8" s="77"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="65">
-        <v>25</v>
-      </c>
-      <c r="G8" s="65">
-        <v>45</v>
-      </c>
-      <c r="H8" s="65">
-        <v>55</v>
-      </c>
-      <c r="I8" s="65">
-        <v>60</v>
-      </c>
-      <c r="J8" s="65">
-        <v>55</v>
-      </c>
-      <c r="K8" s="65">
-        <v>48</v>
-      </c>
-      <c r="L8" s="60">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A9" s="76" t="s">
-        <v>374</v>
-      </c>
-      <c r="B9" s="77"/>
-      <c r="C9" s="61">
-        <v>90</v>
-      </c>
-      <c r="D9" s="61">
-        <v>70</v>
-      </c>
-      <c r="E9" s="61">
-        <v>55</v>
-      </c>
-      <c r="F9" s="61">
-        <v>45</v>
-      </c>
-      <c r="G9" s="61">
-        <v>35</v>
-      </c>
-      <c r="H9" s="61">
-        <v>30</v>
-      </c>
-      <c r="I9" s="61">
-        <v>25</v>
-      </c>
-      <c r="J9" s="61">
-        <v>30</v>
-      </c>
-      <c r="K9" s="61">
-        <v>25</v>
-      </c>
-      <c r="L9" s="60">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A10" s="76" t="s">
-        <v>376</v>
-      </c>
-      <c r="B10" s="77"/>
-      <c r="C10" s="59">
-        <v>50</v>
-      </c>
-      <c r="D10" s="59">
-        <v>40</v>
-      </c>
-      <c r="E10" s="59">
-        <v>35</v>
-      </c>
-      <c r="F10" s="59">
-        <v>30</v>
-      </c>
-      <c r="G10" s="59">
-        <v>30</v>
-      </c>
-      <c r="H10" s="59">
-        <v>30</v>
-      </c>
-      <c r="I10" s="59">
-        <v>30</v>
-      </c>
-      <c r="J10" s="59">
-        <v>35</v>
-      </c>
-      <c r="K10" s="59">
-        <v>33</v>
-      </c>
-      <c r="L10" s="60">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11" s="79" t="s">
-        <v>414</v>
-      </c>
-      <c r="B11" s="80"/>
-      <c r="C11" s="34">
-        <v>440</v>
-      </c>
-      <c r="D11" s="34">
-        <v>560</v>
-      </c>
-      <c r="E11" s="34">
-        <v>555</v>
-      </c>
-      <c r="F11" s="34">
-        <v>565</v>
-      </c>
-      <c r="G11" s="34">
-        <v>575</v>
-      </c>
-      <c r="H11" s="34">
-        <v>565</v>
-      </c>
-      <c r="I11" s="34">
-        <v>535</v>
-      </c>
-      <c r="J11" s="34">
-        <v>380</v>
-      </c>
-      <c r="K11" s="34">
-        <v>229</v>
-      </c>
-      <c r="L11" s="35">
-        <v>4404</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12" s="81" t="s">
-        <v>519</v>
-      </c>
-      <c r="B12" s="82"/>
-      <c r="C12" s="66">
-        <v>775</v>
-      </c>
-      <c r="D12" s="66">
-        <v>775</v>
-      </c>
-      <c r="E12" s="66">
-        <v>775</v>
-      </c>
-      <c r="F12" s="66">
-        <v>930</v>
-      </c>
-      <c r="G12" s="66">
-        <v>930</v>
-      </c>
-      <c r="H12" s="66">
-        <v>930</v>
-      </c>
-      <c r="I12" s="66">
-        <v>930</v>
-      </c>
-      <c r="J12" s="66">
-        <v>930</v>
-      </c>
-      <c r="K12" s="66">
-        <v>930</v>
-      </c>
-      <c r="L12" s="48"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" s="81" t="s">
-        <v>415</v>
-      </c>
-      <c r="B13" s="82"/>
-      <c r="C13" s="66">
-        <v>5</v>
-      </c>
-      <c r="D13" s="66">
-        <v>5</v>
-      </c>
-      <c r="E13" s="66">
-        <v>5</v>
-      </c>
-      <c r="F13" s="66">
-        <v>6</v>
-      </c>
-      <c r="G13" s="66">
-        <v>6</v>
-      </c>
-      <c r="H13" s="66">
-        <v>6</v>
-      </c>
-      <c r="I13" s="66">
-        <v>6</v>
-      </c>
-      <c r="J13" s="66">
-        <v>6</v>
-      </c>
-      <c r="K13" s="66">
-        <v>6</v>
-      </c>
-      <c r="L13" s="48"/>
-    </row>
-    <row r="16" spans="1:12" ht="16" x14ac:dyDescent="0.4">
-      <c r="A16" s="74" t="s">
-        <v>438</v>
-      </c>
-      <c r="B16" s="74"/>
-      <c r="C16" s="74"/>
-      <c r="D16" s="74"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="74"/>
-      <c r="G16" s="74"/>
-      <c r="H16" s="74"/>
-      <c r="I16" s="74"/>
-      <c r="J16" s="74"/>
-      <c r="K16" s="74"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A17" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="B17" s="78"/>
-      <c r="C17" s="34" t="s">
-        <v>402</v>
-      </c>
-      <c r="D17" s="34" t="s">
-        <v>403</v>
-      </c>
-      <c r="E17" s="34" t="s">
-        <v>404</v>
-      </c>
-      <c r="F17" s="34" t="s">
-        <v>405</v>
-      </c>
-      <c r="G17" s="34" t="s">
-        <v>406</v>
-      </c>
-      <c r="H17" s="34" t="s">
-        <v>407</v>
-      </c>
-      <c r="I17" s="34" t="s">
-        <v>408</v>
-      </c>
-      <c r="J17" s="34" t="s">
-        <v>409</v>
-      </c>
-      <c r="K17" s="34" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A18" s="76" t="s">
-        <v>416</v>
-      </c>
-      <c r="B18" s="77"/>
-      <c r="C18" s="67" t="s">
-        <v>417</v>
-      </c>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="46"/>
-      <c r="K18" s="46"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A19" s="76" t="s">
-        <v>439</v>
-      </c>
-      <c r="B19" s="77"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="G19" s="46"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A20" s="76" t="s">
-        <v>395</v>
-      </c>
-      <c r="B20" s="77"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="I20" s="46"/>
-      <c r="J20" s="46"/>
-      <c r="K20" s="46"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A21" s="76" t="s">
-        <v>440</v>
-      </c>
-      <c r="B21" s="77"/>
-      <c r="C21" s="46"/>
-      <c r="D21" s="46"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="12" t="s">
-        <v>417</v>
-      </c>
-      <c r="H21" s="12" t="s">
-        <v>417</v>
-      </c>
-      <c r="I21" s="12" t="s">
-        <v>417</v>
-      </c>
-      <c r="J21" s="46"/>
-      <c r="K21" s="46"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A22" s="76" t="s">
-        <v>441</v>
-      </c>
-      <c r="B22" s="77"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="46"/>
-      <c r="H22" s="15" t="s">
-        <v>417</v>
-      </c>
-      <c r="I22" s="15" t="s">
-        <v>417</v>
-      </c>
-      <c r="J22" s="15" t="s">
-        <v>417</v>
-      </c>
-      <c r="K22" s="46"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A23" s="76" t="s">
-        <v>442</v>
-      </c>
-      <c r="B23" s="77"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="68" t="s">
-        <v>417</v>
-      </c>
-      <c r="J23" s="68" t="s">
-        <v>417</v>
-      </c>
-      <c r="K23" s="68" t="s">
-        <v>417</v>
-      </c>
+      <c r="K26" s="63"/>
+      <c r="L26" s="63"/>
+      <c r="M26" s="63"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
